--- a/data/01-31-densitycutter.xlsx
+++ b/data/01-31-densitycutter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\Messung1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/819f14cd63a8f0d1/Masterarbeit-Jil_Lehnert/01-31-Messung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD349A19-14F9-4926-A7E2-D17B5C1466C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{CD349A19-14F9-4926-A7E2-D17B5C1466C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1217F728-87DC-4414-88DF-4B05703C8536}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -38,28 +38,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Dichtewert2</t>
-  </si>
-  <si>
-    <t>Dichtewert3</t>
-  </si>
-  <si>
-    <t>Abweichung</t>
-  </si>
-  <si>
-    <t>Abweichung 2</t>
-  </si>
-  <si>
-    <t>Dichtewert1 in kg/m^3</t>
-  </si>
-  <si>
     <t>snowdepth</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>snowheighth</t>
+    <t>snowheight</t>
+  </si>
+  <si>
+    <t>density1 in kg/m^3</t>
+  </si>
+  <si>
+    <t>density2</t>
+  </si>
+  <si>
+    <t>density3</t>
+  </si>
+  <si>
+    <t>deviation in %</t>
+  </si>
+  <si>
+    <t>deviation 2</t>
   </si>
 </sst>
 </file>
@@ -436,28 +436,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">

--- a/data/01-31-densitycutter.xlsx
+++ b/data/01-31-densitycutter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/819f14cd63a8f0d1/Masterarbeit-Jil_Lehnert/01-31-Messung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{CD349A19-14F9-4926-A7E2-D17B5C1466C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1217F728-87DC-4414-88DF-4B05703C8536}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FE3B28-621B-4CD6-954C-875E84E334D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
+    <workbookView xWindow="-26160" yWindow="1695" windowWidth="21600" windowHeight="10365" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>snowdepth</t>
   </si>
@@ -47,9 +47,6 @@
     <t>snowheight</t>
   </si>
   <si>
-    <t>density1 in kg/m^3</t>
-  </si>
-  <si>
     <t>density2</t>
   </si>
   <si>
@@ -60,6 +57,15 @@
   </si>
   <si>
     <t>deviation 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> in kg/m^3</t>
+  </si>
+  <si>
+    <t>density1</t>
+  </si>
+  <si>
+    <t>density4</t>
   </si>
 </sst>
 </file>
@@ -431,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1CA8-A778-4AE0-A87F-1DE4A1FF0877}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,25 +448,31 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -473,16 +485,16 @@
       <c r="D2">
         <v>113</v>
       </c>
-      <c r="F2">
-        <f>ABS(D2 - C2) / C2 * 100</f>
+      <c r="G2">
+        <f t="shared" ref="G2:G11" si="0">ABS(D2 - C2) / C2 * 100</f>
         <v>3.4188034188034191</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <f>AVERAGE(C2:E2)</f>
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>17</v>
       </c>
@@ -495,16 +507,16 @@
       <c r="D3">
         <v>113</v>
       </c>
-      <c r="F3">
-        <f>ABS(D3 - C3) / C3 * 100</f>
+      <c r="G3">
+        <f t="shared" si="0"/>
         <v>3.4188034188034191</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <f>AVERAGE(C3:E3)</f>
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>32</v>
       </c>
@@ -517,16 +529,16 @@
       <c r="D4">
         <v>146</v>
       </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F11" si="0">ABS(D4 - C4) / C4 * 100</f>
+      <c r="G4">
+        <f t="shared" si="0"/>
         <v>1.3888888888888888</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <f>AVERAGE(C4:E4)</f>
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>45</v>
       </c>
@@ -539,16 +551,16 @@
       <c r="D5">
         <v>180</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>1.1235955056179776</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <f>AVERAGE(C5:E5)</f>
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>48</v>
       </c>
@@ -564,20 +576,20 @@
       <c r="E6">
         <v>280</v>
       </c>
-      <c r="F6">
-        <f>ABS(D6 - C6) / C6 * 100</f>
+      <c r="G6">
+        <f t="shared" si="0"/>
         <v>3.125</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <f>ABS(E6 - C6) / C6 * 100</f>
         <v>2.7777777777777777</v>
       </c>
-      <c r="H6">
-        <f t="shared" ref="H6:H11" si="1">AVERAGE(C6:F6)</f>
-        <v>212.53125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6">
+        <f>AVERAGE(C6:E6)</f>
+        <v>282.33333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>68</v>
       </c>
@@ -590,16 +602,16 @@
       <c r="D7">
         <v>270</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>1.1235955056179776</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>179.374531835206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7">
+        <f>AVERAGE(C7:D7)</f>
+        <v>268.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>74</v>
       </c>
@@ -612,16 +624,16 @@
       <c r="D8">
         <v>312</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>0.32154340836012862</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>207.77384780278672</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8">
+        <f>AVERAGE(C8:D8)</f>
+        <v>311.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>84</v>
       </c>
@@ -634,16 +646,16 @@
       <c r="D9">
         <v>363</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9">
+        <f>AVERAGE(C9:D9)</f>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>89</v>
       </c>
@@ -656,16 +668,16 @@
       <c r="D10">
         <v>294</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>2.4390243902439024</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
-        <v>194.47967479674799</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10">
+        <f>AVERAGE(C10:D10)</f>
+        <v>290.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>118</v>
       </c>
@@ -678,13 +690,13 @@
       <c r="D11">
         <v>288</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>0.69930069930069927</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
-        <v>191.56643356643357</v>
+      <c r="I11">
+        <f>AVERAGE(C11:D11)</f>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
